--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_01_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_01_18_Cau.xlsx
@@ -921,7 +921,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt chưa quan sát được với chắc chắn không tồn tại.</t>
+          <t>Trong quy trình nghiên cứu Jobs-to-be-Done (JTBD), nếu chưa có bằng chứng quan sát được người dùng thực hiện một bước (như bước Điều chỉnh), nhóm phải đánh dấu bước đó là chưa áp dụng hoặc chưa có bằng chứng và tiếp tục khảo sát; tuyệt đối không tự tiện giữ bước đó như một sự thật chỉ vì biểu mẫu chuẩn có 7 bước.</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách giá trị 0 đã được định nghĩa khỏi trường hợp không có quan sát.</t>
+          <t>Đối với dữ liệu có giá trị thiếu (missing values) và số 0 được từ điển dữ liệu định nghĩa rõ là 'không hữu ích': (a) Giá trị 0 là một điểm số hợp lệ, không được quy đổi thành missing; (b) Cần phân tích xem dữ liệu thiếu có xuất hiện phi ngẫu nhiên (MNAR/MAR) theo nhóm hay thời điểm; (d) Khi báo cáo kết quả bắt buộc phải công bố mẫu số thực tế và phương pháp xử lý missing data. Không được tự ý gán 38% missing thành 0 hoặc giả định phần không thiếu đại diện cho toàn bộ mẫu.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_01_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_01_18_Cau.xlsx
@@ -672,10 +672,20 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách người yêu cầu, người quyết định và người thực hiện mua.
-Phân tích theo nguyên lý thiết kế: Tách người yêu cầu, người quyết định và người thực hiện mua.</t>
+- 1.0 điểm: Xác định chính xác Người thực hiện công việc phù hợp là Quản lý (Approving Manager).
+- 1.0 điểm: Loại bỏ đúng vai trò Nhân viên tạo yêu cầu kèm lý giải họ là người yêu cầu, không phải người quyết định.
+- 1.0 điểm: Loại bỏ đúng vai trò Kế toán kèm lý giải họ là người thực hiện mua/chi tiền sau phê duyệt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định Người thực hiện công việc phù hợp (Job Executor):
+- Người thực hiện công việc cốt lõi: Quản lý trực tiếp / Người phê duyệt (Approving Manager).
+- Lý do: Công việc chính được xác định là 'quyết định có phê duyệt một khoản chi hay không'. Người nắm quyền hạn, chịu trách nhiệm pháp lý và ngân sách để đưa ra phán quyết đồng ý hay từ chối khoản chi chính là Quản lý.
+2. Loại bỏ hai vai trò không trực tiếp thực hiện công việc này và lý giải:
+- Loại vai trò 'Nhân viên tạo yêu cầu' (Requisitioner / Employee): Nhân viên là người khởi tạo nhu cầu chi tiêu (Job Beneficiary / Requester), công việc của họ là 'gửi yêu cầu thanh toán để được hoàn tiền', chứ họ không có thẩm quyền hay trách nhiệm thực hiện việc 'quyết định phê duyệt'.
+- Loại vai trò 'Kế toán mua gói phần mềm' (Buyer / Procurement / Accountant): Kế toán hoặc bộ phận mua sắm là người thực hiện mua bán hoặc chi tiền sau khi đã có phê duyệt (Job Enabler / Purchaser), họ chỉ thực thi hành động giao dịch tài chính, không phải là người ra quyết định đánh giá tính hợp lý nghiệp vụ để phê duyệt khoản chi.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong lý thuyết Jobs-to-be-Done (JTBD), việc xác định đúng Người thực hiện công việc (Job Executor) là tối quan trọng. Cần bóc tách rõ rệt giữa: Người yêu cầu (Requester), Người ra quyết định (Decision Maker/Job Executor), và Người thực thi kỹ thuật/mua hàng (Purchaser/Enabler). Thiết kế sản phẩm AI cho người duyệt chi phải tập trung vào hỗ trợ quản lý đánh giá rủi ro và chính sách, chứ không phải các tính năng nhập liệu của nhân viên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Tony Ulwick - Jobs to be Done: Theory to Practice &amp; Strategyn JTBD Framework (https://strategyn.com/jobs-to-be-done/)</t>
         </is>
       </c>
     </row>
@@ -752,10 +762,21 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết điều người dùng muốn hoàn tất, không viết công cụ họ dùng.
-Phân tích theo nguyên lý thiết kế: Viết điều người dùng muốn hoàn tất, không viết công cụ họ dùng.</t>
+- 1.0 điểm: Viết phát biểu công việc chính độc lập hoàn toàn với giải pháp và công nghệ.
+- 1.0 điểm: Tuân thủ đúng cấu trúc chuẩn JTBD: Động từ + Đối tượng ngữ cảnh + Ngữ cảnh làm rõ.
+- 1.0 điểm: Đạt mức độ trừu tượng phù hợp (đánh giá ứng viên phù hợp, không quá hẹp cũng không quá rộng).
+- 1.0 điểm: Giải thích sâu sắc lý do không dùng 'lọc CV bằng AI' (phân biệt giữa công việc trường tồn và công nghệ tạm thời).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phát biểu Công việc Chính độc lập với giải pháp (Solution-Independent Core Job Statement):
+'Đánh giá và xác định các ứng viên đủ điều kiện nhất cho vị trí công việc tuyển dụng trong thời gian ngắn nhất có thể.'
+2. Cấu trúc chuẩn hóa của phát biểu: [Động từ hành động: Đánh giá và xác định] + [Đối tượng ngữ cảnh: các ứng viên đủ điều kiện nhất cho vị trí công việc] + [Ngữ cảnh/Mục tiêu: trong thời gian ngắn nhất có thể].
+3. Giải thích vì sao TUYỆT ĐỐI KHÔNG DÙNG cụm từ 'lọc CV bằng AI':
+- 'Lọc CV bằng AI' là một Giải pháp công nghệ (Technology Solution / Implementation Mechanism), hoàn toàn không phải là Bản chất công việc của người dùng (Customer Job).
+- Công việc cốt lõi của nhà tuyển dụng là tìm được người tài phù hợp cho công ty. Họ đã làm công việc này từ hàng chục năm trước bằng hồ sơ giấy, sau đó chuyển sang bảng tính Excel, và hiện nay có thể dùng AI. Nếu công nghệ AI mai sau bị thay thế bởi một mô hình đánh giá năng lực thực tế qua mạng lưới (Skill Network), công việc cốt lõi của họ vẫn không hề thay đổi. Đưa từ khóa 'bằng AI' vào phát biểu sẽ giam cầm tư duy sản phẩm vào công nghệ bề mặt và che khuất mục tiêu thực sự của khách hàng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một Core Job Statement chuẩn mực theo lý thuyết JTBD của Christensen và Ulwick luôn phải độc lập 100% với giải pháp và công nghệ. Khách hàng không 'mua máy khoan 5mm hay máy khoan AI', họ 'cần một cái lỗ 5mm trên tường'. Nhà tuyển dụng cần tìm đúng người phù hợp nhanh nhất; AI chỉ là một phương tiện tạm thời phục vụ mục tiêu đó.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Clayton Christensen - Competing Against Luck: The Story of Innovation and Customer Choice &amp; Strategyn Job Statement Rules (https://hbswk.hbs.edu/item/clay-christensen-the-theory-of-jobs-to-be-done)</t>
         </is>
       </c>
     </row>
@@ -786,10 +807,21 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi vế lấy đúng một phần từ quan sát: tình huống, động lực, kết quả mong muốn.
-Phân tích theo nguyên lý thiết kế: Mỗi vế lấy đúng một phần từ quan sát: tình huống, động lực, kết quả mong muốn.</t>
+- 1.0 điểm: Tuân thủ hoàn hảo cấu trúc cú pháp 3 vế 'Khi... tôi muốn... để có thể...'.
+- 1.0 điểm: Vế tình huống (Khi) lấy chính xác từ bối cảnh trước bài kiểm tra và nhớ mang máng ví dụ attention.
+- 1.0 điểm: Vế động lực (tôi muốn) lấy chính xác từ mong muốn mở đúng đoạn video bài giảng.
+- 1.0 điểm: Vế kết quả (để có thể) thể hiện rõ ràng mục đích kiểm tra cách tính toán và chuẩn bị thi.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Soạn thảo Tình huống Công việc (Job Story) theo cấu trúc chuẩn mực:
+"Khi chuẩn bị bước vào bài kiểm tra và nhớ rằng có ví dụ về cơ chế attention trong video bài giảng nhưng không nhớ chính xác ở phân đoạn nào, tôi muốn định vị và mở ngay đúng đoạn ghi hình có chứa ví dụ đó, để có thể kiểm tra lại từng bước tính toán chi tiết và tự tin làm bài thi đạt điểm cao."
+Bóc tách sự tương ứng chặt chẽ với từng phần của dữ kiện quan sát thực tế:
+1. Tình huống bối cảnh (When - Context): 'Khi chuẩn bị bước vào bài kiểm tra và nhớ có ví dụ về attention nhưng không nhớ nằm ở video nào' -&gt; Trích xuất trực tiếp từ quan sát Lan trước kỳ thi.
+2. Động lực / Mong muốn hành động (I want to - Motivation): 'tôi muốn định vị và mở ngay đúng đoạn ghi hình có chứa ví dụ đó' -&gt; Trích xuất từ mong muốn thao tác cụ thể của Lan.
+3. Kết quả mong đợi cuối cùng (So I can - Expected Outcome): 'để có thể kiểm tra lại cách tính và làm bài thi đạt kết quả tốt' -&gt; Trích xuất từ giá trị thực tiễn mà Lan hướng tới.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Job Story (khác với User Story truyền thống) tập trung vào Ngữ cảnh kích hoạt (Context), Động lực giải quyết (Motivation) và Kết quả mong đợi (Outcome). Việc bám sát bằng chứng thực tế từ quan sát người dùng giúp Job Story có tính xác thực cao, không bị rơi vào các suy diễn chung chung.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Alan Klement - Designing Features Using Job Stories (Jobs to be Done Framework) (https://www.intercom.com/books/jobs-to-be-done)</t>
         </is>
       </c>
     </row>
@@ -870,10 +902,24 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xóa tên nút/công nghệ trước, rồi dùng động từ–đối tượng.
-Phân tích theo nguyên lý thiết kế: Xóa tên nút/công nghệ trước, rồi dùng động từ–đối tượng.</t>
+- 1.0 điểm: Chẩn đoán chính xác lỗi: mô tả click path nút bấm UI/công nghệ thay vì bản đồ công việc khách quan.
+- 1.0 điểm: Viết lại ít nhất 4 bước độc lập giải pháp chuẩn ngữ pháp [Động từ] - [Đối tượng] cho việc tóm tắt chuẩn bị họp.
+- 1.0 điểm: Các bước bao quát toàn diện chu trình (thu thập, nhận diện trọng tâm, tổng hợp, đối chiếu).
+- 1.0 điểm: Đánh dấu chính xác 1 bước chưa có bằng chứng hoặc không áp dụng theo yêu cầu đề bài.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán Lỗi của bản đồ công việc cũ:
+- Lỗi nghiêm trọng: Nhóm đã mô tả một 'Bản đồ thao tác giao diện trên phần mềm cụ thể' (UI/Feature Click Path) thay vì một 'Bản đồ công việc của người dùng' (Solution-Independent Job Map).
+- Các bước 'Mở ứng dụng', 'bấm Tải lên', 'chờ AI', 'bấm Tải xuống' toàn bộ là tên nút bấm và cơ chế kỹ thuật của phần mềm. Nếu người dùng nhận được tài liệu tóm tắt qua email do trợ lý gửi, toàn bộ 4 bước này biến mất nhưng công việc chuẩn bị họp của họ vẫn diễn ra bình thường.
+2. Viết lại Bản đồ Công việc độc lập với giải pháp (ít nhất 4 bước dạng Động từ - Đối tượng):
+- Bước 1: Thu thập và Lựa chọn tài liệu họp (Locate &amp; Aggregate Meeting Documents).
+- Bước 2: Đọc lướt và Xác định các thông tin trọng tâm cần chú ý (Scan &amp; Identify Key Agendas / Discussion Points).
+- Bước 3: Trích xuất và Tổng hợp các điểm quyết định then chốt thành bản tóm tắt ngắn (Synthesize Core Action Items &amp; Insights).
+- Bước 4: Kiểm tra và Đối chiếu tính chính xác của thông tin tóm tắt với văn bản gốc (Verify Factual Accuracy Against Source).
+- Bước 5 (Đánh dấu trạng thái): Chia sẻ bản tóm tắt cho các thành viên tham gia họp -&gt; ĐÁNH DẤU: [CHƯA CÓ BẰNG CHỨNG / KHÔNG ÁP DỤNG TRONG NGỮ CẢNH CÁ NHÂN TỰ CHUẨN BỊ].
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một Solution-Independent Job Map mô tả hành trình tư duy và công việc phổ quát mà người dùng phải hoàn tất từ lúc bắt đầu đến khi kết thúc, bất kể họ có dùng AI hay không. Việc sử dụng công thức [Động từ hành động] + [Đối tượng ngữ cảnh] giúp đội ngũ nhìn ra những cơ hội hỗ trợ người dùng ở các bước chuẩn bị và đối chiếu mà phần mềm hiện tại chưa đáp ứng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Lance Bettencourt &amp; Anthony Ulwick - The Customer-Centered Innovation Map (Harvard Business Review) (https://strategyn.com/jobs-to-be-done/)</t>
         </is>
       </c>
     </row>
@@ -1006,10 +1052,26 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hãy thử để một người khác áp quy tắc mà không biết ý định của nhóm.
-Phân tích theo nguyên lý thiết kế: Hãy thử để một người khác áp quy tắc mà không biết ý định của nhóm.</t>
+- 1.0 điểm: Soạn thảo Quy tắc đưa vào (Inclusion) rõ ràng, bao quát các dạng chào hỏi, cảm thán, than phiền mơ hồ.
+- 1.0 điểm: Soạn thảo Quy tắc loại trừ (Exclusion) cụ thể đối với các câu hỏi có từ nghi vấn và nội dung tra cứu rõ.
+- 1.0 điểm: Xử lý dứt khoát tình huống 'hả' được đưa vào mã 'không phải câu hỏi rõ' kèm lập luận thuyết phục.
+- 1.0 điểm: Tiêu chí đảm bảo tính tái hiện cao (Inter-coder reliability): người khác áp dụng vẫn cho kết quả như nhau.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Xây dựng Sổ tay Quy tắc Mã hóa Định tính (Qualitative Pattern Codebook) cho mẫu 'Tin nhắn không phải câu hỏi rõ':
+1. Quy tắc Đưa vào (Inclusion Criteria):
+- Đưa vào mã này nếu tin nhắn của người dùng thuộc một trong các trường hợp sau:
+  + Chỉ chứa từ chào hỏi xã giao đơn thuần hoặc biểu tượng cảm xúc (ví dụ: 'hii', 'hello', 'alo', icon mặt cười) mà không kèm theo bất kỳ yêu cầu nội dung nào.
+  + Tin nhắn chỉ là từ ngữ thể hiện cảm thán, ngạc nhiên, hoặc phản ứng mơ hồ ngắn dưới 3 từ mà không có chủ ngữ, vị ngữ hoặc đối tượng truy vấn xác định (ví dụ: 'hả', 'ủa', 'gì vậy').
+  + Tin nhắn là câu trần thuật hoặc than phiền chung chung về tình trạng bản thân mà không chứa từ để hỏi hoặc yêu cầu hỗ trợ cụ thể (ví dụ: 'em không hiểu attention' - đây là phát biểu trạng thái, chưa nêu rõ câu hỏi cần giải thích khía cạnh nào: công thức, code hay trực giác).
+2. Quy tắc Loại trừ (Exclusion Criteria):
+- LOẠI TRỪ (Không được gán mã này) đối với bất kỳ tin nhắn nào có chứa từ nghi vấn tường minh (như 'hỏi', 'khi nào', 'ở đâu', 'như thế nào', dấu chấm hỏi '?') hoặc yêu cầu một thông tin cụ thể có thể tra cứu được trong hệ thống (ví dụ: 'cho em hỏi lịch học?', 'bài nộp lúc nào?').
+3. Quy tắc Xử lý Tình huống 'hả' (Borderline Case Resolution):
+- Quyết định mã hóa: Tin nhắn 'hả' ĐƯỢC GÁN VÀO MÃ 'Tin nhắn không phải câu hỏi rõ' (Inclusion).
+- Biện minh: 'hả' chỉ là một thán từ phản ứng mang tính bối rối cục bộ, độ dài 1 từ, hoàn toàn không có đối tượng thông tin và không thể hiện bất kỳ nội dung nghiệp vụ nào để trợ giảng AI có thể trả lời trực tiếp. Người chấm độc lập khi áp dụng quy tắc đưa vào sẽ xếp 'hả' vào nhóm phản ứng mơ hồ mà không có bất kỳ sự tranh cãi nào.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong nghiên cứu định tính và kiểm toán hội thoại AI, một Codebook (sổ tay mã hóa) xuất sắc phải mang tính khách quan có thể tái hiện. Quy tắc đưa vào và loại trừ phải rõ ràng đến mức một người chấm độc lập không quen biết dự án vẫn có thể phân loại đồng nhất các trường hợp nhập nhằng như thán từ 'hả'.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Johnny Saldaña - The Coding Manual for Qualitative Researchers &amp; Content Analysis Methodologies (https://methods.sagepub.com/book/the-coding-manual-for-qualitative-researchers)</t>
         </is>
       </c>
     </row>
@@ -1040,10 +1102,25 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mẫu dùng để tính không còn là 200 nếu ba tình huống bị loại khỏi cả tử và mẫu.
-Phân tích theo nguyên lý thiết kế: Mẫu dùng để tính không còn là 200 nếu ba tình huống bị loại khỏi cả tử và mẫu.</t>
+- 1.0 điểm: Xác định chính xác mẫu số thực dùng là 197 (200 - 3 hội thoại mơ hồ).
+- 1.0 điểm: Xác định chính xác tử số là 18 hội thoại.
+- 1.0 điểm: Tính toán đúng tỷ lệ phổ biến: 18/197 ≈ 9,14%.
+- 1.0 điểm: Giải thích rõ ràng nguyên tắc kiểm toán: không chia cho 200 khi đã loại trừ 3 trường hợp khỏi không gian mẫu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định Mẫu số thực dùng (Actual Valid Denominator):
+- Tổng số hội thoại ban đầu: 200 hội thoại.
+- Số hội thoại mơ hồ bị loại khỏi cả tử và mẫu: 3 hội thoại.
+- Mẫu số thực tế sử dụng để tính toán: `Mẫu số = 200 - 3 = 197 hội thoại`.
+2. Xác định Tử số hợp lệ (Valid Numerator):
+- Số hội thoại có ít nhất một tin nhắn mở đầu không phải câu hỏi rõ theo quy tắc đã khóa: 18 hội thoại.
+3. Báo cáo Tỷ lệ có thể kiểm lại được (Reproducible Prevalence Rate):
+- Tỷ lệ phổ biến (Prevalence Rate) = `18 / 197 ≈ 0,09137` hay **9,14%** (hoặc trình bày dưới dạng phân số chuẩn kiểm toán: `18/197`).
+4. Cảnh báo tính minh bạch khoa học:
+Tuyệt đối không được lấy 18 chia cho 200 (= 9,0%), vì 3 hội thoại mơ hồ đã bị loại bỏ khỏi không gian mẫu hợp lệ. Việc báo cáo rõ ràng mẫu số 197 và tử số 18 kèm quy tắc lọc giúp bất kỳ kiểm toán viên độc lập nào cũng có thể tái lập và xác minh lại con số 9,14% một cách nhất quán.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong dịch tễ học và kiểm toán thống kê sản phẩm AI, khi các trường hợp không đủ điều kiện (Out-of-scope / Ambiguous) bị loại bỏ khỏi nghiên cứu, chúng bắt buộc phải bị trừ khỏi cả Tử số và Mẫu số. Báo cáo tỷ lệ phổ biến (Prevalence) phải luôn công bố mẫu số thực dùng để bảo đảm tính toàn vẹn và khả năng tái lập của dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Epidemiological Prevalence Measurement Standards &amp; Statistical Principles for AI Quality Auditing (https://www.cdc.gov/csels/dsepd/ss1978/lesson3/section2.html)</t>
         </is>
       </c>
     </row>
@@ -1122,10 +1199,25 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tử và mẫu phải cùng loại đơn vị.
-Phân tích theo nguyên lý thiết kế: Tử và mẫu phải cùng loại đơn vị.</t>
+- 1.0 điểm: Chẩn đoán chính xác lỗi lẫn lộn đơn vị: lấy sự kiện (lỗi) chia cho thực thể (hội thoại) rồi gán nhãn phần trăm.
+- 1.0 điểm: Khẳng định dứt khoát tỷ lệ phần trăm hội thoại có lỗi không thể vượt quá 100%.
+- 1.0 điểm: Đề xuất Chỉ số 1 hợp lệ: Tỷ lệ hội thoại có lỗi (Defect Conversation Rate &lt;= 100%).
+- 1.0 điểm: Đề xuất Chỉ số 2 hợp lệ: Mật độ lỗi trung bình trên mỗi hội thoại (Defect Density = 65/50 = 1.3 lỗi/hội thoại).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán Lỗi Đơn vị và Lỗi Mẫu số (Unit of Analysis &amp; Denominator Fallacy):
+- Bản chất lỗi: Nhóm nghiên cứu đã phạm sai lầm nghiêm trọng về 'Lẫn lộn đơn vị phân tích' (Unit of Analysis Mismatch). Tử số là 'số lượng sự kiện lỗi' (Event level: 65 lỗi), trong khi mẫu số lại là 'số lượng thực thể hội thoại' (Entity level: 50 hội thoại).
+- Khi một cuộc hội thoại có thể chứa nhiều lỗi đồng thời (1-to-many relationship), việc lấy tổng số lỗi chia cho tổng số hội thoại rồi gán ký hiệu phần trăm (%) và kết luận '130% hội thoại có lỗi' là hoàn toàn sai về mặt toán học và xác suất. Tỷ lệ phần trăm các hội thoại có lỗi theo định nghĩa xác suất không bao giờ có thể vượt quá 100%.
+2. Đề xuất Hai chỉ số Hợp lệ riêng biệt:
+- Chỉ số 1: Tỷ lệ Hội thoại bị Lỗi (Defect Conversation Rate - Tỷ lệ phần trăm thực thể):
+  + Công thức: `(Số hội thoại có ít nhất 1 lỗi / Tổng số 50 hội thoại) * 100%`.
+  + Ý nghĩa: Đo lường xác suất một người dùng gặp phải trải nghiệm lỗi khi mở hội thoại (giá trị chuẩn nằm trong khoảng từ 0% đến 100%, ví dụ: nếu 30/50 hội thoại có lỗi thì tỷ lệ là 60%).
+- Chỉ số 2: Mật độ Lỗi Trung bình trên mỗi Hội thoại (Average Defect Density per Conversation - Tần suất sự kiện):
+  + Công thức: `Tổng số lỗi / Tổng số hội thoại = 65 / 50 = 1,30 lỗi / hội thoại`.
+  + Ý nghĩa: Đo lường mức độ nghiêm trọng và số lượng lỗi trung bình phát sinh trong một cuộc hội thoại, không dùng ký hiệu phần trăm (%).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Lỗi '130% hội thoại có lỗi' là minh chứng kinh điển của việc vi phạm nguyên tắc đồng nhất đơn vị phân tích (Unit of Analysis). Một chỉ số tỷ lệ (Rate) phải có tử số là tập con của mẫu số. Nếu đo đếm tần suất sự kiện lặp lại trên mỗi đối tượng, chỉ số bắt buộc phải được biểu diễn dưới dạng Mật độ (Density - lỗi/hội thoại) chứ không phải Phần trăm (%).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Principles - Metrics That Matter &amp; Software Quality Engineering Defect Metrics (IEEE Standards) (https://sre.google/sre-book/table-of-contents/)</t>
         </is>
       </c>
     </row>
@@ -1204,10 +1296,29 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm số lượng bản ghi ghép tương ứng trước và sau khi nối dữ liệu.
-Phân tích theo nguyên lý thiết kế: Kiểm số lượng bản ghi ghép tương ứng trước và sau khi nối dữ liệu.</t>
+- 1.0 điểm: Chỉ ra chính xác lỗi bùng nổ bản ghi quan hệ 1-N (Join Fan-out / Cartesian multiplication).
+- 1.0 điểm: Giải thích rõ lý do số tin nhắn tăng gấp 3 là do mỗi hội thoại có trung bình 3 lượt ratings nhân bản dòng.
+- 1.0 điểm: Đề xuất giải pháp kỹ thuật đúng đắn: đếm độc lập trên bảng messages hoặc dùng `COUNT(DISTINCT message_id)`.
+- 1.0 điểm: Đề xuất quy trình tiền tổng hợp (pre-aggregation) bảng ratings để duy trì quan hệ 1-1.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Kiểm tra Lỗi Kỹ thuật khi Nối Dữ liệu (Cartesian Fan-Out / Join Explosion Audit):
+- Bản chất lỗi: Hiện tượng bùng nổ quan hệ Một-Nhiều (1-to-Many Fan-Out). Bảng `messages` chứa các tin nhắn của một cuộc hội thoại. Bảng `ratings` chứa nhiều dòng đánh giá cho cùng một `conversation_id` (quan hệ 1 hội thoại có N đánh giá).
+- Khi thực hiện phép ghép trực tiếp (Direct SQL JOIN: `messages JOIN ratings ON conversation_id`), mỗi tin nhắn trong bảng `messages` sẽ bị nhân bản lên N lần tương ứng với số dòng đánh giá trong bảng `ratings`. Điều này giải thích chính xác vì sao tổng số lượng tin nhắn đếm được đột ngột tăng gấp ba (do trung bình mỗi hội thoại có 3 bản ghi đánh giá).
+2. Cách tạo Chỉ số Số lượng Tin nhắn Hợp lệ:
+- Phương pháp 1: Đếm trên bảng gốc độc lập không qua JOIN:
+  ```sql
+  SELECT COUNT(message_id) AS total_messages FROM messages;
+  ```
+- Phương pháp 2: Sử dụng toán tử khử trùng lặp nếu bắt buộc phải query từ bảng đã join:
+  ```sql
+  SELECT COUNT(DISTINCT message_id) AS total_unique_messages FROM joined_table;
+  ```
+- Phương pháp 3: Tiền tổng hợp (Pre-aggregation) bảng `ratings` trước khi join:
+  Thu gọn bảng `ratings` theo `conversation_id` (ví dụ: lấy trung bình rating) thành quan hệ 1-1 trước khi thực hiện LEFT JOIN với bảng `messages`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiểm toán dữ liệu sản phẩm AI, hiện tượng Fan-Out khi JOIN bảng là nguyên nhân hàng đầu làm sai lệch toàn bộ các chỉ số volume và tỷ lệ lỗi. Việc kiểm tra số lượng bản ghi trước và sau khi JOIN (Pre/Post-join record count verification) là quy tắc kiểm toán bắt buộc đối với mọi kỹ sư dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Data Engineering Best Practices &amp; SQL Join Integrity Patterns in Analytics Warehouses (https://principles.design/)</t>
         </is>
       </c>
     </row>
@@ -1344,10 +1455,24 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết sao cho TA có thể kiểm bằng mắt và thao tác.
-Phân tích theo nguyên lý thiết kế: Viết sao cho TA có thể kiểm bằng mắt và thao tác.</t>
+- 1.0 điểm: Đặc tả nguyên tắc G8 với vị trí cụ thể (góc trên phải) và hành động người dùng (phím Esc hoặc nút X).
+- 1.0 điểm: Hệ thống thực thi G8 tức thì (&lt;100ms), không có modal cản trở, focus vào khung gõ tay.
+- 1.0 điểm: Đặc tả nguyên tắc G11 với vị trí trực quan (bên cạnh câu trả lời) và hành động rê chuột/bấm xem.
+- 1.0 điểm: Hệ thống thực thi G11 hiển thị trích dẫn tài liệu cụ thể (slide, trang, mục) kèm link đối chiếu trực tiếp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Đặc tả Hành vi Giao diện có thể Kiểm tra cho Hai Nguyên tắc Human-AI Guidelines:
+1. Nguyên tắc G8: 'Gạt bỏ Dễ dàng' (Support Efficient Dismissal):
+- Vị trí trên giao diện: Nằm ở góc trên bên phải của khung gợi ý câu trả lời AI (hộp gợi ý đề xuất màu xám nhạt đặt ngay dưới câu hỏi của sinh viên).
+- Hành vi người dùng: TA chỉ cần bấm 1 phím tắt duy nhất (phím `Esc`) hoặc bấm vào biểu tượng dấu chữ 'X' nhỏ (nút Gạt bỏ) trên khung gợi ý.
+- Hành vi hệ thống quan sát được: Khung gợi ý của AI lập tức biến mất hoàn toàn trong vòng &lt;100ms mà không hiển thị thêm bất kỳ hộp thoại xác nhận phiền hà nào ('Bạn có chắc muốn tắt không?'). Con trỏ chuột tự động focus vào khung nhập liệu trống để TA tự gõ câu trả lời của mình mà không bị gián đoạn.
+2. Nguyên tắc G11: 'Giải thích Vì sao' (Make Clear Why the System Did What It Did):
+- Vị trí trên giao diện: Nằm ở góc dưới bên trái của khung gợi ý câu trả lời, bên cạnh nút chấp nhận.
+- Hành vi người dùng: TA rê chuột (hover) vào dòng chữ nhỏ 'Căn cứ gợi ý' hoặc bấm vào biểu tượng bóng đèn / dấu chấm hỏi.
+- Hành vi hệ thống quan sát được: Một bảng popover hiển thị trực quan trích dẫn nguồn tri thức: 'Gợi ý này được trích xuất từ Slide bài giảng Tuần 4 (Trang 12, Mục 2.3 về Ma trận Attention) và FAQ khóa học #45', kèm đường link cho phép TA nhấp chuột để mở trực tiếp tài liệu gốc đối chiếu trong 1 giây.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Các nguyên tắc tương tác người - AI (Microsoft Human-AI Guidelines) như G8 (Dismissal) và G11 (Explanation) không được dừng lại ở lý thuyết trừu tượng mà phải được hiện thực hóa thành các thành phần giao diện cụ thể có thể kiểm thử thao tác: vị trí đặt nút, phím tắt thao tác, tốc độ phản hồi và nội dung bằng chứng trích dẫn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Microsoft Research - Guidelines for Human-AI Interaction (Amershi et al., 2019) - G8 &amp; G11 (https://www.microsoft.com/en-us/research/project/guidelines-for-human-ai-interaction/)</t>
         </is>
       </c>
     </row>
